--- a/card_data.xlsx
+++ b/card_data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cpyh\godot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A522D7-02C0-4F2A-9663-A2EA1A814787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B34CB6-8EDD-4DD6-91E0-77B7CC273EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="2745" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3300" yWindow="2745" windowWidth="21600" windowHeight="11175" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="人物" sheetId="1" r:id="rId1"/>
     <sheet name="资源" sheetId="4" r:id="rId2"/>
-    <sheet name="装备" sheetId="2" r:id="rId3"/>
+    <sheet name="道具" sheetId="2" r:id="rId3"/>
     <sheet name="防具" sheetId="5" r:id="rId4"/>
     <sheet name="遗物" sheetId="3" r:id="rId5"/>
   </sheets>
